--- a/artfynd/A 72326-2021 artfynd.xlsx
+++ b/artfynd/A 72326-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 72326-2021 artfynd.xlsx
+++ b/artfynd/A 72326-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,113 +1350,6 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>112605434</v>
-      </c>
-      <c r="B7" t="n">
-        <v>78946</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Risberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>728699</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7192686</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Norsjö</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Norsjö</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 72326-2021 artfynd.xlsx
+++ b/artfynd/A 72326-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6803431</v>
+        <v>112605434</v>
       </c>
       <c r="B2" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,52 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>storbäcken, Vb</t>
+          <t>Risberg, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729732.4712969258</v>
+        <v>728699</v>
       </c>
       <c r="R2" t="n">
-        <v>7192285.441698131</v>
+        <v>7192686</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,27 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-06-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-06-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>förekommer i fuktstråk i äldre granskog längs storbäcken</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,81 +762,75 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>fuktstråk i äldre granskog omkring storbäcken</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mikael Marberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mikael Marberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6803307</v>
+        <v>6803279</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1365</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>storbäcken, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729813.2748242758</v>
+        <v>729813</v>
       </c>
       <c r="R3" t="n">
-        <v>7192204.280184632</v>
+        <v>7192204</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -893,27 +857,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-06-17</t>
+          <t>2013-06-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-06-17</t>
+          <t>2013-06-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Förekommer på äldre sälgar söder om myren och österut längs storbäcken.</t>
+          <t>över 300 blommande</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,24 +889,14 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>vanlig sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea subsp. caprea</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>äldre sälgar i avsatt granskog längs bäck och våtmark</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Salix caprea subsp. caprea # äldre sälgar i avsatt granskog längs bäck och våtmark</t>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>genomsilande markvatten i äldre bäcknära granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -960,15 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6803316</v>
+        <v>6803307</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,31 +925,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1010,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729732.4712969258</v>
+        <v>729813</v>
       </c>
       <c r="R4" t="n">
-        <v>7192285.441698131</v>
+        <v>7192204</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1040,27 +985,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2013-06-18</t>
+          <t>2013-06-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2013-06-18</t>
+          <t>2013-06-17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>funnen på två granlågor</t>
+          <t>Förekommer på äldre sälgar söder om myren och österut längs storbäcken.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1069,13 +1014,27 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>äldre granskog med fuktstråk som avsatts längs bäck</t>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>vanlig sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea subsp. caprea</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>äldre sälgar i avsatt granskog längs bäck och våtmark</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Salix caprea subsp. caprea # äldre sälgar i avsatt granskog längs bäck och våtmark</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1093,15 +1052,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6803279</v>
+        <v>6803431</v>
       </c>
       <c r="B5" t="n">
-        <v>99882</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,31 +1063,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1365</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1148,10 +1102,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729813</v>
+        <v>729732</v>
       </c>
       <c r="R5" t="n">
-        <v>7192204</v>
+        <v>7192285</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1183,7 +1137,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1193,12 +1147,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>över 300 blommande</t>
+          <t>förekommer i fuktstråk i äldre granskog längs storbäcken</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1212,12 +1166,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Högörtgranskog</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>genomsilande markvatten i äldre bäcknära granskog</t>
+          <t>fuktstråk i äldre granskog omkring storbäcken</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1232,123 +1186,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>109910753</v>
-      </c>
-      <c r="B6" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Risberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>728699.2894223372</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7192686.04447869</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Norsjö</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Norsjö</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
